--- a/Faculties/Natural Science/Experimental/Undergrad Modules Natural Science.xlsx
+++ b/Faculties/Natural Science/Experimental/Undergrad Modules Natural Science.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Natural Science/Experimental/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwamb\OneDrive\Desktop\Team_6_repo\Team19\Faculties\Natural Science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_F25DC773A252ABDACC10480281DB6CA25BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF7F342D-BBA6-4B42-BE53-55DB529872BC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5B13A2-E277-46FD-BB1A-78FD402507AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12084" yWindow="2064" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1140,27 +1140,6 @@
     <t>PHY212/217, MAT105/103/152</t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Environment and Water Science  3331 ,BSc Applied Geology Extended  3011 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Applied Geology Extended  3011 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biodiversity and Conservation Biology  3217 ,BSc Environment and Water Science  3331 ,BSc Biodiversity and Conservation Biology Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSC141, LSC142 (or LFS151, LFS152  AND CHE114 (or CHE124, CHE116, CHM126 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biodiversity and Conservation Biology  3217 ,BSc Biodiversity and Conservation Biology Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Medical Bioscience  3230 </t>
-  </si>
-  <si>
     <t xml:space="preserve">CHE114/124, LSC141/142 (or LFS/MBS equivalents </t>
   </si>
   <si>
@@ -1170,117 +1149,42 @@
     <t xml:space="preserve">CHE114/124, LSC141/142 (or equivalents </t>
   </si>
   <si>
-    <t xml:space="preserve">Bachelor of Pharmacy  3305 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biotechnology  3211 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Chemistry 114 (N </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Physical Science  3233 ,Bachelor of Pharmacy  3305 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Chemistry 116 (N </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Medical Bioscience  3230 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Chemistry 124 (N </t>
   </si>
   <si>
     <t xml:space="preserve">Chemistry 126 (N </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Physical Science  3233 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Chemical Sciences  3220 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Chemical Sciences  3220 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biotechnology  3211 ,BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Medical Bioscience  3230 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Mathematics and Statistical Sciences  3227 </t>
-  </si>
-  <si>
     <t xml:space="preserve">ECO151 (or ECO241 </t>
   </si>
   <si>
     <t xml:space="preserve">ECO152 (or equivalent </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Medical Bioscience  3230 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Computer Science  3221 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Medical Bioscience  3230 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Physical Science  3233 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Environment and Water Science  3331 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Environment and Water Science  3331 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Computer Science  3221 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Applied Geology Extended  3011 ,BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Life Sciences 151 (SF </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Biodiversity Extended  3015 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Life Sciences 152 (SF </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Environment and Water Science  3331 ,BSc Medical Bioscience  3230 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Chemical Sciences  3220 ,BSc Environment and Water Science  3331 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Mathematics 115 (N </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biotechnology  3211 ,Bachelor of Pharmacy  3305 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Mathematics 151 (SF </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology Extended  3011 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Chemical Sciences  3220 ,BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
     <t xml:space="preserve">MAT105 (or equivalent </t>
   </si>
   <si>
     <t xml:space="preserve">APM112, MAT105 (or equivalent </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Medical Bioscience  3230 </t>
-  </si>
-  <si>
     <t xml:space="preserve">CHE114, CHE124, PCH233/ (min 40% in PCH233 </t>
   </si>
   <si>
@@ -1293,40 +1197,22 @@
     <t xml:space="preserve">PHC213, PHC223, PHC313/ (min 40% for PHC313 </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Applied Geology  3214 ,BSc Biotechnology  3211 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Physics 151 (SF </t>
   </si>
   <si>
     <t xml:space="preserve">Physics 152 (SF </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Chemical Sciences  3220 ,BSc Computer Science  3221 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Computer Science  3221 ,BSc Physical Science  3233 </t>
-  </si>
-  <si>
     <t xml:space="preserve">PCE231, PHC213, PPR214/ (min 40% in each </t>
   </si>
   <si>
     <t xml:space="preserve">PPR214, PPR224, PPR314 (min 40% </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Computer Science  3221 ,BSc Environment and Water Science  3331 ,BSc Mathematics and Statistical Sciences  3227 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSc Computer Science  3221 ,BSc Mathematics and Statistical Sciences  3227 </t>
-  </si>
-  <si>
     <t xml:space="preserve">STA111/125/151 (or equivalent </t>
   </si>
   <si>
-    <t xml:space="preserve">BSc Biodiversity  3217 ,BSc Biotechnology  3211 ,BSc Environment and Water Science  3331 ,BSc Medical Bioscience  3230 </t>
-  </si>
-  <si>
-    <t>MAT105 (or equivalent  AND STA111/125/151</t>
+    <t xml:space="preserve">Statistics 151 (SF </t>
   </si>
   <si>
     <t xml:space="preserve">STA211 (qualified for exam </t>
@@ -1335,7 +1221,121 @@
     <t xml:space="preserve"> General Science Elective </t>
   </si>
   <si>
-    <t>Statistics 151</t>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Environment and Water Science 3331 ,BSc Applied Geology Extended 3011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Applied Geology Extended 3011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Mathematics and Statistical Sciences 3227 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity and Conservation Biology 3217 ,BSc Environment and Water Science 3331 ,BSc Biodiversity and Conservation Biology Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSC141, LSC142 (or LFS151, LFS152 AND CHE114 (or CHE124, CHE116, CHM126 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity and Conservation Biology 3217 ,BSc Biodiversity and Conservation Biology Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biotechnology 3211 ,BSc Chemical Sciences 3220 ,BSc Medical Bioscience 3230 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor of Pharmacy 3305 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biotechnology 3211 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Chemical Sciences 3220 ,BSc Physical Science 3233 ,Bachelor of Pharmacy 3305 ,BSc Applied Geology Extended 3011 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Environment and Water Science 3331 ,BSc Medical Bioscience 3230 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Chemical Sciences 3220 ,BSc Physical Science 3233 ,BSc Applied Geology Extended 3011 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences 3220 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences 3220 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science 3221 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biotechnology 3211 ,BSc Computer Science 3221 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Medical Bioscience 3230 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Mathematics and Statistical Sciences 3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Environment and Water Science 3331 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Medical Bioscience 3230 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Computer Science 3221 ,BSc Environment and Water Science 3331 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Medical Bioscience 3230 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Environment and Water Science 3331 ,BSc Physical Science 3233 ,BSc Applied Geology Extended 3011 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biodiversity 3217 ,BSc Environment and Water Science 3331 ,BSc Applied Geology Extended 3011 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Environment and Water Science 3331 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Environment and Water Science 3331 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science 3221 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology Extended 3011 ,BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity Extended 3015 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Chemical Sciences 3220 ,BSc Environment and Water Science 3331 ,BSc Medical Bioscience 3230 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Chemical Sciences 3220 ,BSc Environment and Water Science 3331 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biotechnology 3211 ,Bachelor of Pharmacy 3305 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology Extended 3011 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences 3220 ,BSc Computer Science 3221 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Medical Bioscience 3230 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Applied Geology 3214 ,BSc Biotechnology 3211 ,BSc Environment and Water Science 3331 ,BSc Mathematics and Statistical Sciences 3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Chemical Sciences 3220 ,BSc Computer Science 3221 ,BSc Environment and Water Science 3331 ,BSc Mathematics and Statistical Sciences 3227 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science 3221 ,BSc Physical Science 3233 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Computer Science 3221 ,BSc Environment and Water Science 3331 ,BSc Mathematics and Statistical Sciences 3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Computer Science 3221 ,BSc Mathematics and Statistical Sciences 3227 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSc Biodiversity 3217 ,BSc Biotechnology 3211 ,BSc Environment and Water Science 3331 ,BSc Medical Bioscience 3230 </t>
+  </si>
+  <si>
+    <t>MAT105 (or equivalent AND STA111/125/151</t>
   </si>
 </sst>
 </file>
@@ -1709,7 +1709,7 @@
         <v>354</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
@@ -1729,7 +1729,7 @@
         <v>354</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -1749,7 +1749,7 @@
         <v>354</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>9</v>
@@ -1769,7 +1769,7 @@
         <v>355</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
@@ -1789,7 +1789,7 @@
         <v>355</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>19</v>
@@ -1809,7 +1809,7 @@
         <v>355</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>19</v>
@@ -1829,7 +1829,7 @@
         <v>355</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>19</v>
@@ -1849,7 +1849,7 @@
         <v>356</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>6</v>
@@ -1869,7 +1869,7 @@
         <v>356</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>6</v>
@@ -1889,7 +1889,7 @@
         <v>354</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>31</v>
@@ -1909,7 +1909,7 @@
         <v>354</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>31</v>
@@ -1929,7 +1929,7 @@
         <v>354</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>36</v>
@@ -1949,10 +1949,10 @@
         <v>354</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
@@ -1969,7 +1969,7 @@
         <v>355</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>34</v>
@@ -1989,7 +1989,7 @@
         <v>355</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>43</v>
@@ -2009,7 +2009,7 @@
         <v>355</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>46</v>
@@ -2029,7 +2029,7 @@
         <v>355</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>49</v>
@@ -2049,10 +2049,10 @@
         <v>354</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
@@ -2069,10 +2069,10 @@
         <v>354</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>6</v>
@@ -2089,10 +2089,10 @@
         <v>354</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -2109,7 +2109,7 @@
         <v>354</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>6</v>
@@ -2129,10 +2129,10 @@
         <v>354</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>6</v>
@@ -2149,10 +2149,10 @@
         <v>354</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
@@ -2169,10 +2169,10 @@
         <v>354</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>6</v>
@@ -2189,7 +2189,7 @@
         <v>355</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>66</v>
@@ -2209,7 +2209,7 @@
         <v>355</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>66</v>
@@ -2229,7 +2229,7 @@
         <v>355</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>66</v>
@@ -2249,7 +2249,7 @@
         <v>355</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>66</v>
@@ -2263,13 +2263,13 @@
         <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>6</v>
@@ -2283,13 +2283,13 @@
         <v>74</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>6</v>
@@ -2303,13 +2303,13 @@
         <v>75</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>6</v>
@@ -2323,13 +2323,13 @@
         <v>76</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>6</v>
@@ -2349,7 +2349,7 @@
         <v>354</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>79</v>
@@ -2369,7 +2369,7 @@
         <v>354</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>79</v>
@@ -2389,7 +2389,7 @@
         <v>354</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>79</v>
@@ -2409,7 +2409,7 @@
         <v>355</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>86</v>
@@ -2429,7 +2429,7 @@
         <v>355</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>86</v>
@@ -2449,7 +2449,7 @@
         <v>355</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>91</v>
@@ -2469,7 +2469,7 @@
         <v>355</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>91</v>
@@ -2489,7 +2489,7 @@
         <v>356</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>6</v>
@@ -2509,7 +2509,7 @@
         <v>356</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>6</v>
@@ -2529,7 +2529,7 @@
         <v>356</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>6</v>
@@ -2549,7 +2549,7 @@
         <v>354</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>94</v>
@@ -2569,7 +2569,7 @@
         <v>354</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>94</v>
@@ -2589,7 +2589,7 @@
         <v>355</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>106</v>
@@ -2609,7 +2609,7 @@
         <v>355</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>106</v>
@@ -2629,7 +2629,7 @@
         <v>356</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>6</v>
@@ -2649,7 +2649,7 @@
         <v>356</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>6</v>
@@ -2669,10 +2669,10 @@
         <v>354</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2689,10 +2689,10 @@
         <v>354</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2709,10 +2709,10 @@
         <v>354</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2729,7 +2729,7 @@
         <v>354</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>357</v>
@@ -2749,7 +2749,7 @@
         <v>355</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>119</v>
@@ -2769,7 +2769,7 @@
         <v>355</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>113</v>
@@ -2789,7 +2789,7 @@
         <v>355</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>115</v>
@@ -2809,7 +2809,7 @@
         <v>355</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>129</v>
@@ -2829,7 +2829,7 @@
         <v>355</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>129</v>
@@ -2849,7 +2849,7 @@
         <v>355</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>115</v>
@@ -2869,7 +2869,7 @@
         <v>356</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>6</v>
@@ -2889,7 +2889,7 @@
         <v>356</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>6</v>
@@ -2909,7 +2909,7 @@
         <v>356</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>6</v>
@@ -2929,7 +2929,7 @@
         <v>356</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>6</v>
@@ -2949,7 +2949,7 @@
         <v>354</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>9</v>
@@ -2969,7 +2969,7 @@
         <v>354</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>9</v>
@@ -2989,7 +2989,7 @@
         <v>354</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>9</v>
@@ -3009,7 +3009,7 @@
         <v>355</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>151</v>
@@ -3029,7 +3029,7 @@
         <v>355</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>151</v>
@@ -3049,7 +3049,7 @@
         <v>355</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>148</v>
@@ -3069,7 +3069,7 @@
         <v>355</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>151</v>
@@ -3089,7 +3089,7 @@
         <v>356</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>6</v>
@@ -3109,7 +3109,7 @@
         <v>356</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>6</v>
@@ -3129,7 +3129,7 @@
         <v>356</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>6</v>
@@ -3149,7 +3149,7 @@
         <v>354</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>358</v>
@@ -3169,7 +3169,7 @@
         <v>354</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>164</v>
@@ -3189,7 +3189,7 @@
         <v>355</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>359</v>
@@ -3209,7 +3209,7 @@
         <v>355</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>168</v>
@@ -3229,7 +3229,7 @@
         <v>356</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>6</v>
@@ -3243,13 +3243,13 @@
         <v>174</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>6</v>
@@ -3263,13 +3263,13 @@
         <v>175</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>6</v>
@@ -3289,7 +3289,7 @@
         <v>356</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>6</v>
@@ -3309,7 +3309,7 @@
         <v>356</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>6</v>
@@ -3323,13 +3323,13 @@
         <v>180</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>6</v>
@@ -3349,7 +3349,7 @@
         <v>356</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>6</v>
@@ -3363,13 +3363,13 @@
         <v>182</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>412</v>
+        <v>383</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>6</v>
@@ -3389,7 +3389,7 @@
         <v>356</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>6</v>
@@ -3409,10 +3409,10 @@
         <v>354</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -3429,10 +3429,10 @@
         <v>354</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>185</v>
@@ -3449,7 +3449,7 @@
         <v>354</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>6</v>
@@ -3469,10 +3469,10 @@
         <v>354</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -3489,7 +3489,7 @@
         <v>355</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>185</v>
@@ -3509,7 +3509,7 @@
         <v>355</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>197</v>
@@ -3529,7 +3529,7 @@
         <v>355</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>189</v>
@@ -3549,7 +3549,7 @@
         <v>355</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>197</v>
@@ -3569,7 +3569,7 @@
         <v>356</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>6</v>
@@ -3589,7 +3589,7 @@
         <v>356</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>6</v>
@@ -3609,7 +3609,7 @@
         <v>354</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>208</v>
@@ -3629,7 +3629,7 @@
         <v>354</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>208</v>
@@ -3649,7 +3649,7 @@
         <v>355</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>362</v>
@@ -3669,7 +3669,7 @@
         <v>355</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>363</v>
@@ -3689,7 +3689,7 @@
         <v>354</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>176</v>
@@ -3709,7 +3709,7 @@
         <v>354</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>215</v>
@@ -3729,7 +3729,7 @@
         <v>355</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>364</v>
@@ -3749,7 +3749,7 @@
         <v>355</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>364</v>
@@ -3769,7 +3769,7 @@
         <v>354</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>225</v>
@@ -3789,7 +3789,7 @@
         <v>354</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>225</v>
@@ -3809,7 +3809,7 @@
         <v>355</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>230</v>
@@ -3829,7 +3829,7 @@
         <v>355</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>233</v>
@@ -3849,7 +3849,7 @@
         <v>365</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>236</v>
@@ -3869,7 +3869,7 @@
         <v>365</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>236</v>
@@ -3889,10 +3889,10 @@
         <v>354</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>6</v>
@@ -3909,7 +3909,7 @@
         <v>354</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>79</v>
@@ -3929,7 +3929,7 @@
         <v>355</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>245</v>
@@ -3949,10 +3949,10 @@
         <v>355</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>419</v>
+        <v>387</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -3969,7 +3969,7 @@
         <v>365</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>250</v>
@@ -3989,7 +3989,7 @@
         <v>356</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>6</v>
@@ -4009,7 +4009,7 @@
         <v>365</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>255</v>
@@ -4029,7 +4029,7 @@
         <v>365</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>6</v>
@@ -4049,7 +4049,7 @@
         <v>365</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>260</v>
@@ -4069,7 +4069,7 @@
         <v>356</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>160</v>
@@ -4089,7 +4089,7 @@
         <v>354</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>265</v>
@@ -4109,10 +4109,10 @@
         <v>354</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>420</v>
+        <v>388</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>6</v>
@@ -4129,7 +4129,7 @@
         <v>355</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>270</v>
@@ -4149,10 +4149,10 @@
         <v>355</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>6</v>
@@ -4169,7 +4169,7 @@
         <v>365</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>275</v>
@@ -4189,7 +4189,7 @@
         <v>365</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>255</v>
@@ -4209,7 +4209,7 @@
         <v>365</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>280</v>
@@ -4229,7 +4229,7 @@
         <v>365</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>283</v>
@@ -4249,7 +4249,7 @@
         <v>365</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>286</v>
@@ -4269,7 +4269,7 @@
         <v>365</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>275</v>
@@ -4289,7 +4289,7 @@
         <v>356</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>6</v>
@@ -4309,7 +4309,7 @@
         <v>356</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>6</v>
@@ -4329,7 +4329,7 @@
         <v>356</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>6</v>
@@ -4349,7 +4349,7 @@
         <v>356</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>6</v>
@@ -4369,7 +4369,7 @@
         <v>356</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>6</v>
@@ -4383,13 +4383,13 @@
         <v>299</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>6</v>
@@ -4403,13 +4403,13 @@
         <v>300</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>354</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>6</v>
@@ -4429,7 +4429,7 @@
         <v>354</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>367</v>
@@ -4449,7 +4449,7 @@
         <v>354</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>6</v>
@@ -4469,7 +4469,7 @@
         <v>354</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>368</v>
@@ -4489,7 +4489,7 @@
         <v>354</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>369</v>
@@ -4509,7 +4509,7 @@
         <v>355</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>312</v>
@@ -4529,7 +4529,7 @@
         <v>355</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>308</v>
@@ -4549,7 +4549,7 @@
         <v>355</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>312</v>
@@ -4569,7 +4569,7 @@
         <v>355</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>370</v>
@@ -4589,7 +4589,7 @@
         <v>354</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>321</v>
@@ -4609,10 +4609,10 @@
         <v>354</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>427</v>
+        <v>392</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>266</v>
@@ -4629,7 +4629,7 @@
         <v>355</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>326</v>
@@ -4649,10 +4649,10 @@
         <v>355</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4669,7 +4669,7 @@
         <v>365</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>331</v>
@@ -4689,7 +4689,7 @@
         <v>365</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>331</v>
@@ -4709,7 +4709,7 @@
         <v>365</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>331</v>
@@ -4729,7 +4729,7 @@
         <v>356</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>6</v>
@@ -4749,13 +4749,13 @@
         <v>356</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -4769,7 +4769,7 @@
         <v>356</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>6</v>
@@ -4783,13 +4783,13 @@
         <v>342</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>356</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>6</v>
@@ -4809,10 +4809,10 @@
         <v>354</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>6</v>
@@ -4829,10 +4829,10 @@
         <v>354</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>434</v>
+        <v>396</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>6</v>
@@ -4849,7 +4849,7 @@
         <v>355</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>349</v>
@@ -4869,7 +4869,7 @@
         <v>355</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>349</v>
@@ -4889,7 +4889,7 @@
         <v>356</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>435</v>
+        <v>397</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>6</v>
